--- a/docs/payhome_finance_kpi.xlsx
+++ b/docs/payhome_finance_kpi.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次P_L" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週次KPIレポート" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次レビュー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ活用ロードマップ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求テンプレート" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求管理" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次P_L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週次KPIレポート" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次レビュー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ活用ロードマップ" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方ガイド" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +61,13 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8740C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003D2200"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +128,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,6 +502,1733 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ぺいほーむ 請求管理台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>※ フリー会計で請求書を発行。本シートは経理部共有用の請求記録台帳です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>請求月</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>企業名</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>企業担当者名</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>企業住所</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>請求日</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>支払期限</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>品目</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>金額（税抜）</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>消費税</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>合計（税込）</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>フリー会計
+請求書No.</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>入金状況</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>入金日</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>入金額</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>差額</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>（工務店名）</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>（担当者名）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>プラットフォーム掲載料（スタンダード）</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K5" s="11">
+        <f>I5*J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="11">
+        <f>K5*0.1</f>
+        <v/>
+      </c>
+      <c r="M5" s="11">
+        <f>K5+L5</f>
+        <v/>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>未請求</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="11" t="inlineStr"/>
+      <c r="R5" s="11">
+        <f>M5-Q5</f>
+        <v/>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>（工務店名）</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>（担当者名）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>ルームツアー動画撮影・制作</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <f>I6*J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="11">
+        <f>K6*0.1</f>
+        <v/>
+      </c>
+      <c r="M6" s="11">
+        <f>K6+L6</f>
+        <v/>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>未請求</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="11" t="inlineStr"/>
+      <c r="R6" s="11">
+        <f>M6-Q6</f>
+        <v/>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>（工務店名）</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>（担当者名）</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>リード送客費（反響課金）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K7" s="11">
+        <f>I7*J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="11">
+        <f>K7*0.1</f>
+        <v/>
+      </c>
+      <c r="M7" s="11">
+        <f>K7+L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>未請求</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="11" t="inlineStr"/>
+      <c r="R7" s="11">
+        <f>M7-Q7</f>
+        <v/>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13">
+        <f>I8*J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="13">
+        <f>K8*0.1</f>
+        <v/>
+      </c>
+      <c r="M8" s="13">
+        <f>K8+L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="12" t="n"/>
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="13">
+        <f>M8-Q8</f>
+        <v/>
+      </c>
+      <c r="S8" s="12" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13">
+        <f>I9*J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="13">
+        <f>K9*0.1</f>
+        <v/>
+      </c>
+      <c r="M9" s="13">
+        <f>K9+L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="13">
+        <f>M9-Q9</f>
+        <v/>
+      </c>
+      <c r="S9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="13">
+        <f>I10*J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="13">
+        <f>K10*0.1</f>
+        <v/>
+      </c>
+      <c r="M10" s="13">
+        <f>K10+L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13">
+        <f>M10-Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="13">
+        <f>I11*J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>K11*0.1</f>
+        <v/>
+      </c>
+      <c r="M11" s="13">
+        <f>K11+L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="13" t="n"/>
+      <c r="R11" s="13">
+        <f>M11-Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13">
+        <f>I12*J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="13">
+        <f>K12*0.1</f>
+        <v/>
+      </c>
+      <c r="M12" s="13">
+        <f>K12+L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="13" t="n"/>
+      <c r="R12" s="13">
+        <f>M12-Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13">
+        <f>I13*J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="13">
+        <f>K13*0.1</f>
+        <v/>
+      </c>
+      <c r="M13" s="13">
+        <f>K13+L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="13" t="n"/>
+      <c r="R13" s="13">
+        <f>M13-Q13</f>
+        <v/>
+      </c>
+      <c r="S13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="13">
+        <f>I14*J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="13">
+        <f>K14*0.1</f>
+        <v/>
+      </c>
+      <c r="M14" s="13">
+        <f>K14+L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="13">
+        <f>M14-Q14</f>
+        <v/>
+      </c>
+      <c r="S14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="13">
+        <f>I15*J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="13">
+        <f>K15*0.1</f>
+        <v/>
+      </c>
+      <c r="M15" s="13">
+        <f>K15+L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+      <c r="P15" s="12" t="n"/>
+      <c r="Q15" s="13" t="n"/>
+      <c r="R15" s="13">
+        <f>M15-Q15</f>
+        <v/>
+      </c>
+      <c r="S15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13">
+        <f>I16*J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="13">
+        <f>K16*0.1</f>
+        <v/>
+      </c>
+      <c r="M16" s="13">
+        <f>K16+L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13">
+        <f>M16-Q16</f>
+        <v/>
+      </c>
+      <c r="S16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="13">
+        <f>I17*J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="13">
+        <f>K17*0.1</f>
+        <v/>
+      </c>
+      <c r="M17" s="13">
+        <f>K17+L17</f>
+        <v/>
+      </c>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="13" t="n"/>
+      <c r="R17" s="13">
+        <f>M17-Q17</f>
+        <v/>
+      </c>
+      <c r="S17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="13" t="n"/>
+      <c r="K18" s="13">
+        <f>I18*J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="13">
+        <f>K18*0.1</f>
+        <v/>
+      </c>
+      <c r="M18" s="13">
+        <f>K18+L18</f>
+        <v/>
+      </c>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
+      <c r="P18" s="12" t="n"/>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="13">
+        <f>M18-Q18</f>
+        <v/>
+      </c>
+      <c r="S18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13">
+        <f>I19*J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="13">
+        <f>K19*0.1</f>
+        <v/>
+      </c>
+      <c r="M19" s="13">
+        <f>K19+L19</f>
+        <v/>
+      </c>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="13">
+        <f>M19-Q19</f>
+        <v/>
+      </c>
+      <c r="S19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="13">
+        <f>I20*J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="13">
+        <f>K20*0.1</f>
+        <v/>
+      </c>
+      <c r="M20" s="13">
+        <f>K20+L20</f>
+        <v/>
+      </c>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="12" t="n"/>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="13">
+        <f>M20-Q20</f>
+        <v/>
+      </c>
+      <c r="S20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="13">
+        <f>I21*J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="13">
+        <f>K21*0.1</f>
+        <v/>
+      </c>
+      <c r="M21" s="13">
+        <f>K21+L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="12" t="n"/>
+      <c r="Q21" s="13" t="n"/>
+      <c r="R21" s="13">
+        <f>M21-Q21</f>
+        <v/>
+      </c>
+      <c r="S21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="13">
+        <f>I22*J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="13">
+        <f>K22*0.1</f>
+        <v/>
+      </c>
+      <c r="M22" s="13">
+        <f>K22+L22</f>
+        <v/>
+      </c>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
+      <c r="P22" s="12" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13">
+        <f>M22-Q22</f>
+        <v/>
+      </c>
+      <c r="S22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="13">
+        <f>I23*J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="13">
+        <f>K23*0.1</f>
+        <v/>
+      </c>
+      <c r="M23" s="13">
+        <f>K23+L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="13" t="n"/>
+      <c r="R23" s="13">
+        <f>M23-Q23</f>
+        <v/>
+      </c>
+      <c r="S23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="13">
+        <f>I24*J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="13">
+        <f>K24*0.1</f>
+        <v/>
+      </c>
+      <c r="M24" s="13">
+        <f>K24+L24</f>
+        <v/>
+      </c>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13">
+        <f>M24-Q24</f>
+        <v/>
+      </c>
+      <c r="S24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13">
+        <f>I25*J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="13">
+        <f>K25*0.1</f>
+        <v/>
+      </c>
+      <c r="M25" s="13">
+        <f>K25+L25</f>
+        <v/>
+      </c>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="13" t="n"/>
+      <c r="R25" s="13">
+        <f>M25-Q25</f>
+        <v/>
+      </c>
+      <c r="S25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="13">
+        <f>I26*J26</f>
+        <v/>
+      </c>
+      <c r="L26" s="13">
+        <f>K26*0.1</f>
+        <v/>
+      </c>
+      <c r="M26" s="13">
+        <f>K26+L26</f>
+        <v/>
+      </c>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13">
+        <f>M26-Q26</f>
+        <v/>
+      </c>
+      <c r="S26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="13">
+        <f>I27*J27</f>
+        <v/>
+      </c>
+      <c r="L27" s="13">
+        <f>K27*0.1</f>
+        <v/>
+      </c>
+      <c r="M27" s="13">
+        <f>K27+L27</f>
+        <v/>
+      </c>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="13" t="n"/>
+      <c r="R27" s="13">
+        <f>M27-Q27</f>
+        <v/>
+      </c>
+      <c r="S27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="13">
+        <f>I28*J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="13">
+        <f>K28*0.1</f>
+        <v/>
+      </c>
+      <c r="M28" s="13">
+        <f>K28+L28</f>
+        <v/>
+      </c>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="13">
+        <f>M28-Q28</f>
+        <v/>
+      </c>
+      <c r="S28" s="12" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="13" t="n"/>
+      <c r="K29" s="13">
+        <f>I29*J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="13">
+        <f>K29*0.1</f>
+        <v/>
+      </c>
+      <c r="M29" s="13">
+        <f>K29+L29</f>
+        <v/>
+      </c>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="13" t="n"/>
+      <c r="R29" s="13">
+        <f>M29-Q29</f>
+        <v/>
+      </c>
+      <c r="S29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="13">
+        <f>I30*J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="13">
+        <f>K30*0.1</f>
+        <v/>
+      </c>
+      <c r="M30" s="13">
+        <f>K30+L30</f>
+        <v/>
+      </c>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="13" t="n"/>
+      <c r="R30" s="13">
+        <f>M30-Q30</f>
+        <v/>
+      </c>
+      <c r="S30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="13">
+        <f>I31*J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="13">
+        <f>K31*0.1</f>
+        <v/>
+      </c>
+      <c r="M31" s="13">
+        <f>K31+L31</f>
+        <v/>
+      </c>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
+      <c r="P31" s="12" t="n"/>
+      <c r="Q31" s="13" t="n"/>
+      <c r="R31" s="13">
+        <f>M31-Q31</f>
+        <v/>
+      </c>
+      <c r="S31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="13" t="n"/>
+      <c r="K32" s="13">
+        <f>I32*J32</f>
+        <v/>
+      </c>
+      <c r="L32" s="13">
+        <f>K32*0.1</f>
+        <v/>
+      </c>
+      <c r="M32" s="13">
+        <f>K32+L32</f>
+        <v/>
+      </c>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
+      <c r="P32" s="12" t="n"/>
+      <c r="Q32" s="13" t="n"/>
+      <c r="R32" s="13">
+        <f>M32-Q32</f>
+        <v/>
+      </c>
+      <c r="S32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="13" t="n"/>
+      <c r="K33" s="13">
+        <f>I33*J33</f>
+        <v/>
+      </c>
+      <c r="L33" s="13">
+        <f>K33*0.1</f>
+        <v/>
+      </c>
+      <c r="M33" s="13">
+        <f>K33+L33</f>
+        <v/>
+      </c>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="12" t="n"/>
+      <c r="P33" s="12" t="n"/>
+      <c r="Q33" s="13" t="n"/>
+      <c r="R33" s="13">
+        <f>M33-Q33</f>
+        <v/>
+      </c>
+      <c r="S33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="13" t="n"/>
+      <c r="K34" s="13">
+        <f>I34*J34</f>
+        <v/>
+      </c>
+      <c r="L34" s="13">
+        <f>K34*0.1</f>
+        <v/>
+      </c>
+      <c r="M34" s="13">
+        <f>K34+L34</f>
+        <v/>
+      </c>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
+      <c r="P34" s="12" t="n"/>
+      <c r="Q34" s="13" t="n"/>
+      <c r="R34" s="13">
+        <f>M34-Q34</f>
+        <v/>
+      </c>
+      <c r="S34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="13" t="n"/>
+      <c r="K35" s="13">
+        <f>I35*J35</f>
+        <v/>
+      </c>
+      <c r="L35" s="13">
+        <f>K35*0.1</f>
+        <v/>
+      </c>
+      <c r="M35" s="13">
+        <f>K35+L35</f>
+        <v/>
+      </c>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="12" t="n"/>
+      <c r="P35" s="12" t="n"/>
+      <c r="Q35" s="13" t="n"/>
+      <c r="R35" s="13">
+        <f>M35-Q35</f>
+        <v/>
+      </c>
+      <c r="S35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="13" t="n"/>
+      <c r="K36" s="13">
+        <f>I36*J36</f>
+        <v/>
+      </c>
+      <c r="L36" s="13">
+        <f>K36*0.1</f>
+        <v/>
+      </c>
+      <c r="M36" s="13">
+        <f>K36+L36</f>
+        <v/>
+      </c>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
+      <c r="P36" s="12" t="n"/>
+      <c r="Q36" s="13" t="n"/>
+      <c r="R36" s="13">
+        <f>M36-Q36</f>
+        <v/>
+      </c>
+      <c r="S36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="13" t="n"/>
+      <c r="K37" s="13">
+        <f>I37*J37</f>
+        <v/>
+      </c>
+      <c r="L37" s="13">
+        <f>K37*0.1</f>
+        <v/>
+      </c>
+      <c r="M37" s="13">
+        <f>K37+L37</f>
+        <v/>
+      </c>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12" t="n"/>
+      <c r="Q37" s="13" t="n"/>
+      <c r="R37" s="13">
+        <f>M37-Q37</f>
+        <v/>
+      </c>
+      <c r="S37" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>月次請求サマリー（経理部共有用）</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="15" t="n"/>
+      <c r="L40" s="15" t="n"/>
+      <c r="M40" s="15" t="n"/>
+      <c r="N40" s="15" t="n"/>
+      <c r="O40" s="15" t="n"/>
+      <c r="P40" s="15" t="n"/>
+      <c r="Q40" s="15" t="n"/>
+      <c r="R40" s="15" t="n"/>
+      <c r="S40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>請求月</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>請求件数</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>請求合計（税抜）</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>消費税合計</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>請求合計（税込）</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>入金済件数</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>入金済合計</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>未入金合計</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="B42" s="3">
+        <f>COUNTIF(B$5:B$37,A42)</f>
+        <v/>
+      </c>
+      <c r="C42" s="11">
+        <f>SUMIF(B$5:B$37,A42,K$5:K$37)</f>
+        <v/>
+      </c>
+      <c r="D42" s="11">
+        <f>SUMIF(B$5:B$37,A42,L$5:L$37)</f>
+        <v/>
+      </c>
+      <c r="E42" s="11">
+        <f>SUMIF(B$5:B$37,A42,M$5:M$37)</f>
+        <v/>
+      </c>
+      <c r="F42" s="3">
+        <f>COUNTIFS(B$5:B$37,A42,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>SUMIFS(Q$5:Q$37,B$5:B$37,A42,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="H42" s="11">
+        <f>E42-G42</f>
+        <v/>
+      </c>
+      <c r="I42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="B43" s="3">
+        <f>COUNTIF(B$5:B$37,A43)</f>
+        <v/>
+      </c>
+      <c r="C43" s="11">
+        <f>SUMIF(B$5:B$37,A43,K$5:K$37)</f>
+        <v/>
+      </c>
+      <c r="D43" s="11">
+        <f>SUMIF(B$5:B$37,A43,L$5:L$37)</f>
+        <v/>
+      </c>
+      <c r="E43" s="11">
+        <f>SUMIF(B$5:B$37,A43,M$5:M$37)</f>
+        <v/>
+      </c>
+      <c r="F43" s="3">
+        <f>COUNTIFS(B$5:B$37,A43,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>SUMIFS(Q$5:Q$37,B$5:B$37,A43,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="H43" s="11">
+        <f>E43-G43</f>
+        <v/>
+      </c>
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="B44" s="3">
+        <f>COUNTIF(B$5:B$37,A44)</f>
+        <v/>
+      </c>
+      <c r="C44" s="11">
+        <f>SUMIF(B$5:B$37,A44,K$5:K$37)</f>
+        <v/>
+      </c>
+      <c r="D44" s="11">
+        <f>SUMIF(B$5:B$37,A44,L$5:L$37)</f>
+        <v/>
+      </c>
+      <c r="E44" s="11">
+        <f>SUMIF(B$5:B$37,A44,M$5:M$37)</f>
+        <v/>
+      </c>
+      <c r="F44" s="3">
+        <f>COUNTIFS(B$5:B$37,A44,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>SUMIFS(Q$5:Q$37,B$5:B$37,A44,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="H44" s="11">
+        <f>E44-G44</f>
+        <v/>
+      </c>
+      <c r="I44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="B45" s="3">
+        <f>COUNTIF(B$5:B$37,A45)</f>
+        <v/>
+      </c>
+      <c r="C45" s="11">
+        <f>SUMIF(B$5:B$37,A45,K$5:K$37)</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>SUMIF(B$5:B$37,A45,L$5:L$37)</f>
+        <v/>
+      </c>
+      <c r="E45" s="11">
+        <f>SUMIF(B$5:B$37,A45,M$5:M$37)</f>
+        <v/>
+      </c>
+      <c r="F45" s="3">
+        <f>COUNTIFS(B$5:B$37,A45,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>SUMIFS(Q$5:Q$37,B$5:B$37,A45,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="H45" s="11">
+        <f>E45-G45</f>
+        <v/>
+      </c>
+      <c r="I45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+      <c r="B46" s="3">
+        <f>COUNTIF(B$5:B$37,A46)</f>
+        <v/>
+      </c>
+      <c r="C46" s="11">
+        <f>SUMIF(B$5:B$37,A46,K$5:K$37)</f>
+        <v/>
+      </c>
+      <c r="D46" s="11">
+        <f>SUMIF(B$5:B$37,A46,L$5:L$37)</f>
+        <v/>
+      </c>
+      <c r="E46" s="11">
+        <f>SUMIF(B$5:B$37,A46,M$5:M$37)</f>
+        <v/>
+      </c>
+      <c r="F46" s="3">
+        <f>COUNTIFS(B$5:B$37,A46,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>SUMIFS(Q$5:Q$37,B$5:B$37,A46,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="H46" s="11">
+        <f>E46-G46</f>
+        <v/>
+      </c>
+      <c r="I46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="B47" s="3">
+        <f>COUNTIF(B$5:B$37,A47)</f>
+        <v/>
+      </c>
+      <c r="C47" s="11">
+        <f>SUMIF(B$5:B$37,A47,K$5:K$37)</f>
+        <v/>
+      </c>
+      <c r="D47" s="11">
+        <f>SUMIF(B$5:B$37,A47,L$5:L$37)</f>
+        <v/>
+      </c>
+      <c r="E47" s="11">
+        <f>SUMIF(B$5:B$37,A47,M$5:M$37)</f>
+        <v/>
+      </c>
+      <c r="F47" s="3">
+        <f>COUNTIFS(B$5:B$37,A47,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>SUMIFS(Q$5:Q$37,B$5:B$37,A47,O$5:O$37,"入金済")</f>
+        <v/>
+      </c>
+      <c r="H47" s="11">
+        <f>E47-G47</f>
+        <v/>
+      </c>
+      <c r="I47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B48" s="11">
+        <f>SUM(B42:B47)</f>
+        <v/>
+      </c>
+      <c r="C48" s="11">
+        <f>SUM(C42:C47)</f>
+        <v/>
+      </c>
+      <c r="D48" s="11">
+        <f>SUM(D42:D47)</f>
+        <v/>
+      </c>
+      <c r="E48" s="11">
+        <f>SUM(E42:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="11">
+        <f>SUM(F42:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>SUM(G42:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="11">
+        <f>SUM(H42:H47)</f>
+        <v/>
+      </c>
+      <c r="I48" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A40:S40"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="O5:O100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"未請求,請求済,入金済,遅延,一部入金,貸倒"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026年4月,2026年5月,2026年6月,2026年7月,2026年8月,2026年9月,2026年10月,2026年11月,2026年12月,2027年1月,2027年2月,2027年3月"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:H100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"プラットフォーム掲載料（ライト）,プラットフォーム掲載料（スタンダード）,プラットフォーム掲載料（プレミアム）,ルームツアー動画撮影・制作,SNS運用代行,WEB制作・SEO,リード送客費（反響課金）,セミナー参加費,広告・タイアップ,その他"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8740C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -987,7 +2732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00E8740C"/>
@@ -1025,7 +2770,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1251,7 +2995,6 @@
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1280,7 +3023,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -1314,7 +3056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00E8740C"/>
@@ -1351,7 +3093,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1581,7 +3322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BBDEFB"/>
@@ -1786,249 +3527,6 @@
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>AI営業支援の初期リリース</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00E8740C"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>請求書</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>請求先:</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>○○工務店 御中</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>株式会社wazeka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>請求日:</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2026年○月○日</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>鹿児島県鹿児島市○○</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>お支払期限:</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2026年○月末日</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>TEL: xxx-xxxx-xxxx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>登録番号: T○○○○○○○○○○○○○</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>品目</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>単価</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>プラットフォーム掲載料（○月分）</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3">
-        <f>C9*D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>スタンダードプラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>ルームツアー動画撮影・制作</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3">
-        <f>C10*D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>リード送客費（○件×○円）</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3">
-        <f>C11*D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="E12" s="3">
-        <f>SUM(E9:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>消費税（10%）</t>
-        </is>
-      </c>
-      <c r="E13" s="3">
-        <f>E12*0.1</f>
-        <v/>
-      </c>
-      <c r="F13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="E14" s="3">
-        <f>E12+E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="3" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>お振込先</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>○○銀行 ○○支店 普通 ○○○○○○○ カ）ワゼカ</t>
         </is>
       </c>
     </row>
@@ -2062,7 +3560,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>売上・経費・KPI・請求の管理ファイルです。月次の経営判断とデータ活用戦略の意思決定に使用します。</t>
+          <t>請求管理</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>請求記録台帳。企業情報/品目/金額を記録し経理部に共有。月次サマリーで請求・入金状況を一覧化。フリー会計の請求書No.と紐付けて管理。プルダウンで入金状況を管理</t>
         </is>
       </c>
     </row>
